--- a/artfynd/A 35216-2025 artfynd.xlsx
+++ b/artfynd/A 35216-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128543298</v>
       </c>
       <c r="B2" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128543131</v>
       </c>
       <c r="B3" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128544549</v>
       </c>
       <c r="B4" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128544732</v>
       </c>
       <c r="B5" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128543413</v>
       </c>
       <c r="B6" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128542654</v>
       </c>
       <c r="B7" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128544741</v>
       </c>
       <c r="B8" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>128543905</v>
       </c>
       <c r="B9" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>128545438</v>
       </c>
       <c r="B10" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>128543476</v>
       </c>
       <c r="B11" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>128543328</v>
       </c>
       <c r="B12" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>128545473</v>
       </c>
       <c r="B13" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35216-2025 artfynd.xlsx
+++ b/artfynd/A 35216-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128543298</v>
       </c>
       <c r="B2" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128543131</v>
       </c>
       <c r="B3" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128544549</v>
       </c>
       <c r="B4" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128544732</v>
       </c>
       <c r="B5" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128543413</v>
       </c>
       <c r="B6" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128542654</v>
       </c>
       <c r="B7" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>128543905</v>
       </c>
       <c r="B9" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>128545438</v>
       </c>
       <c r="B10" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>128543328</v>
       </c>
       <c r="B12" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>128545473</v>
       </c>
       <c r="B13" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35216-2025 artfynd.xlsx
+++ b/artfynd/A 35216-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128543298</v>
       </c>
       <c r="B2" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128543131</v>
       </c>
       <c r="B3" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128544549</v>
       </c>
       <c r="B4" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128544732</v>
       </c>
       <c r="B5" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128543413</v>
       </c>
       <c r="B6" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128542654</v>
       </c>
       <c r="B7" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>128543905</v>
       </c>
       <c r="B9" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>128545438</v>
       </c>
       <c r="B10" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>128543328</v>
       </c>
       <c r="B12" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>128545473</v>
       </c>
       <c r="B13" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35216-2025 artfynd.xlsx
+++ b/artfynd/A 35216-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128543298</v>
       </c>
       <c r="B2" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128543131</v>
       </c>
       <c r="B3" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128544549</v>
       </c>
       <c r="B4" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128544732</v>
       </c>
       <c r="B5" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128543413</v>
       </c>
       <c r="B6" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128542654</v>
       </c>
       <c r="B7" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>128543905</v>
       </c>
       <c r="B9" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>128545438</v>
       </c>
       <c r="B10" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>128543328</v>
       </c>
       <c r="B12" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>128545473</v>
       </c>
       <c r="B13" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35216-2025 artfynd.xlsx
+++ b/artfynd/A 35216-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128543298</v>
       </c>
       <c r="B2" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128543131</v>
       </c>
       <c r="B3" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128544549</v>
       </c>
       <c r="B4" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128544732</v>
       </c>
       <c r="B5" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128543413</v>
       </c>
       <c r="B6" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128542654</v>
       </c>
       <c r="B7" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>128543905</v>
       </c>
       <c r="B9" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>128545438</v>
       </c>
       <c r="B10" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>128543328</v>
       </c>
       <c r="B12" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>128545473</v>
       </c>
       <c r="B13" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35216-2025 artfynd.xlsx
+++ b/artfynd/A 35216-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128543298</v>
       </c>
       <c r="B2" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128543131</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128544549</v>
       </c>
       <c r="B4" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128544732</v>
       </c>
       <c r="B5" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128543413</v>
       </c>
       <c r="B6" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128542654</v>
       </c>
       <c r="B7" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128544741</v>
       </c>
       <c r="B8" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>128543905</v>
       </c>
       <c r="B9" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>128545438</v>
       </c>
       <c r="B10" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>128543476</v>
       </c>
       <c r="B11" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>128543328</v>
       </c>
       <c r="B12" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>128545473</v>
       </c>
       <c r="B13" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35216-2025 artfynd.xlsx
+++ b/artfynd/A 35216-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128543298</v>
       </c>
       <c r="B2" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128543131</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128544549</v>
       </c>
       <c r="B4" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128544732</v>
       </c>
       <c r="B5" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128543413</v>
       </c>
       <c r="B6" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128542654</v>
       </c>
       <c r="B7" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>128543905</v>
       </c>
       <c r="B9" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>128545438</v>
       </c>
       <c r="B10" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>128543328</v>
       </c>
       <c r="B12" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>128545473</v>
       </c>
       <c r="B13" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35216-2025 artfynd.xlsx
+++ b/artfynd/A 35216-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128543298</v>
       </c>
       <c r="B2" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128543131</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128544549</v>
       </c>
       <c r="B4" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128544732</v>
       </c>
       <c r="B5" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128543413</v>
       </c>
       <c r="B6" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128542654</v>
       </c>
       <c r="B7" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>128543905</v>
       </c>
       <c r="B9" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>128545438</v>
       </c>
       <c r="B10" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>128543328</v>
       </c>
       <c r="B12" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>128545473</v>
       </c>
       <c r="B13" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35216-2025 artfynd.xlsx
+++ b/artfynd/A 35216-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128543298</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128543131</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128544549</v>
       </c>
       <c r="B4" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128544732</v>
       </c>
       <c r="B5" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128543413</v>
       </c>
       <c r="B6" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128542654</v>
       </c>
       <c r="B7" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128544741</v>
       </c>
       <c r="B8" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>128543905</v>
       </c>
       <c r="B9" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>128545438</v>
       </c>
       <c r="B10" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>128543476</v>
       </c>
       <c r="B11" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>128543328</v>
       </c>
       <c r="B12" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>128545473</v>
       </c>
       <c r="B13" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35216-2025 artfynd.xlsx
+++ b/artfynd/A 35216-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128543298</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128543131</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128544549</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128544732</v>
       </c>
       <c r="B5" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128543413</v>
       </c>
       <c r="B6" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128542654</v>
       </c>
       <c r="B7" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>128544741</v>
       </c>
       <c r="B8" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>128543905</v>
       </c>
       <c r="B9" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>128545438</v>
       </c>
       <c r="B10" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>128543476</v>
       </c>
       <c r="B11" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>128543328</v>
       </c>
       <c r="B12" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>128545473</v>
       </c>
       <c r="B13" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35216-2025 artfynd.xlsx
+++ b/artfynd/A 35216-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128543298</v>
       </c>
       <c r="B2" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128543131</v>
       </c>
       <c r="B3" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128544549</v>
       </c>
       <c r="B4" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128544732</v>
       </c>
       <c r="B5" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128543413</v>
       </c>
       <c r="B6" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128542654</v>
       </c>
       <c r="B7" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>128543905</v>
       </c>
       <c r="B9" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>128545438</v>
       </c>
       <c r="B10" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>128543328</v>
       </c>
       <c r="B12" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>128545473</v>
       </c>
       <c r="B13" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35216-2025 artfynd.xlsx
+++ b/artfynd/A 35216-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128543298</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128543131</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128544549</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128544732</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128543413</v>
       </c>
       <c r="B6" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>128542654</v>
       </c>
       <c r="B7" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>128543905</v>
       </c>
       <c r="B9" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>128545438</v>
       </c>
       <c r="B10" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>128543328</v>
       </c>
       <c r="B12" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1859,7 +1859,7 @@
         <v>128545473</v>
       </c>
       <c r="B13" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35216-2025 artfynd.xlsx
+++ b/artfynd/A 35216-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128543298</v>
+        <v>128543476</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>58114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         <v>537493</v>
       </c>
       <c r="R2" t="n">
-        <v>6983652</v>
+        <v>6983653</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,48 +782,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128543131</v>
+        <v>128544741</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537503</v>
+        <v>537453</v>
       </c>
       <c r="R3" t="n">
-        <v>6983631</v>
+        <v>6983650</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128544549</v>
+        <v>128542654</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537465</v>
+        <v>537496</v>
       </c>
       <c r="R4" t="n">
-        <v>6983665</v>
+        <v>6983626</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -959,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128544732</v>
+        <v>128543131</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>537453</v>
+        <v>537503</v>
       </c>
       <c r="R5" t="n">
-        <v>6983650</v>
+        <v>6983631</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1066,7 +1070,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1080,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128543413</v>
+        <v>128543298</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,7 +1145,7 @@
         <v>537493</v>
       </c>
       <c r="R6" t="n">
-        <v>6983653</v>
+        <v>6983652</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1173,7 +1177,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1187,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128542654</v>
+        <v>128543328</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>537496</v>
+        <v>537501</v>
       </c>
       <c r="R7" t="n">
-        <v>6983626</v>
+        <v>6983645</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1280,7 +1284,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1294,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,52 +1321,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128544741</v>
+        <v>128543413</v>
       </c>
       <c r="B8" t="n">
-        <v>57883</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Nörder-Kroktjärnberget, Nörder-Kroktjärnberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537453</v>
+        <v>537493</v>
       </c>
       <c r="R8" t="n">
-        <v>6983650</v>
+        <v>6983653</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,7 +1431,7 @@
         <v>128543905</v>
       </c>
       <c r="B9" t="n">
-        <v>98659</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,10 +1535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128545438</v>
+        <v>128544549</v>
       </c>
       <c r="B10" t="n">
-        <v>98659</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537475</v>
+        <v>537465</v>
       </c>
       <c r="R10" t="n">
-        <v>6983614</v>
+        <v>6983665</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1642,32 +1642,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128543476</v>
+        <v>128544732</v>
       </c>
       <c r="B11" t="n">
-        <v>57883</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1677,13 +1677,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537493</v>
+        <v>537453</v>
       </c>
       <c r="R11" t="n">
-        <v>6983653</v>
+        <v>6983650</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,10 +1749,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128543328</v>
+        <v>128545438</v>
       </c>
       <c r="B12" t="n">
-        <v>98659</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1784,10 +1784,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>537501</v>
+        <v>537475</v>
       </c>
       <c r="R12" t="n">
-        <v>6983645</v>
+        <v>6983614</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,7 +1859,7 @@
         <v>128545473</v>
       </c>
       <c r="B13" t="n">
-        <v>98659</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35216-2025 artfynd.xlsx
+++ b/artfynd/A 35216-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128543476</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128544741</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128542654</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128543131</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128543298</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128543328</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1425,6 +1460,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128543413</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1532,6 +1572,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128543905</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1639,6 +1684,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128544549</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1746,6 +1796,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128544732</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1853,6 +1908,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128545438</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1960,8 +2020,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128545473</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>